--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260618.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260618.xlsx
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2441</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>超豐</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>10,566,000</t>
+          <t>6,426,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,17 +1063,17 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>超豐</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>6,426,000</t>
+          <t>10,566,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>4915</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>致伸</t>
+          <t>群益證</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,483,000</t>
+          <t>29,700,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>群益證</t>
+          <t>致伸</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>29,700,000</t>
+          <t>15,483,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>國泰金</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>7,825,000</t>
+          <t>2,378,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>國泰金</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>2,378,000</t>
+          <t>7,825,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>4,434,675</t>
+          <t>3,047,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>3,047,000</t>
+          <t>4,434,675</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
